--- a/p_parameters/archive_parameters/codebooks/D3_incidence_con_caratterizzazione.xlsx
+++ b/p_parameters/archive_parameters/codebooks/D3_incidence_con_caratterizzazione.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="78">
   <si>
     <t xml:space="preserve">parameter</t>
   </si>
@@ -154,13 +154,21 @@
     <t xml:space="preserve">met</t>
   </si>
   <si>
-    <t xml:space="preserve">Uso di metformina nei 2 anni precedenti la data indice</t>
+    <t xml:space="preserve">Uso di metformina nei 2 anni precedenti la data indice
+component of anyantidiab: met</t>
   </si>
   <si>
     <t xml:space="preserve">antidiabother</t>
   </si>
   <si>
-    <t xml:space="preserve">Uso di altri antidiabetici nei 2 anni precedenti la data indice (esclusa metformina)</t>
+    <t xml:space="preserve">Uso di altri antidiabetici nei 2 anni precedenti la data indice (esclusa metformina)
+component of anyantidiab: antidiabother</t>
+  </si>
+  <si>
+    <t xml:space="preserve">study_drugs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">component of anyantidiab: study_drugs</t>
   </si>
   <si>
     <t xml:space="preserve">med_IHD</t>
@@ -230,6 +238,24 @@
   </si>
   <si>
     <t xml:space="preserve">dia_RENDIS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SGLT2i</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GLP1RA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">tirzepatide</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DPP4i</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DPP4i_SGLT2i</t>
+  </si>
+  <si>
+    <t xml:space="preserve">other_combinations</t>
   </si>
 </sst>
 </file>
@@ -304,17 +330,10 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border diagonalUp="false" diagonalDown="false">
       <left/>
       <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border diagonalUp="false" diagonalDown="false">
-      <left/>
-      <right style="thin"/>
       <top/>
       <bottom/>
       <diagonal/>
@@ -345,7 +364,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="9">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -364,14 +383,6 @@
     </xf>
     <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false" readingOrder="1"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
@@ -467,7 +478,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:D67"/>
+  <dimension ref="A1:D1048576"/>
   <sheetFormatPr defaultColWidth="8.453125" defaultRowHeight="14.25" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="43.09"/>
@@ -494,11 +505,11 @@
       <c r="A2" s="0" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="5" t="s">
+      <c r="B2" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C2" s="0"/>
-      <c r="D2" s="5" t="s">
+      <c r="D2" s="0" t="s">
         <v>6</v>
       </c>
     </row>
@@ -506,11 +517,11 @@
       <c r="A3" s="0" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="5" t="s">
+      <c r="B3" s="2" t="s">
         <v>7</v>
       </c>
       <c r="C3" s="0"/>
-      <c r="D3" s="5" t="s">
+      <c r="D3" s="0" t="s">
         <v>8</v>
       </c>
     </row>
@@ -518,11 +529,11 @@
       <c r="A4" s="0" t="s">
         <v>4</v>
       </c>
-      <c r="B4" s="5" t="s">
+      <c r="B4" s="2" t="s">
         <v>9</v>
       </c>
       <c r="C4" s="0"/>
-      <c r="D4" s="5" t="s">
+      <c r="D4" s="0" t="s">
         <v>10</v>
       </c>
     </row>
@@ -530,11 +541,11 @@
       <c r="A5" s="0" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="5" t="s">
+      <c r="B5" s="2" t="s">
         <v>11</v>
       </c>
       <c r="C5" s="0"/>
-      <c r="D5" s="5" t="s">
+      <c r="D5" s="0" t="s">
         <v>12</v>
       </c>
     </row>
@@ -542,11 +553,11 @@
       <c r="A6" s="0" t="s">
         <v>4</v>
       </c>
-      <c r="B6" s="6" t="s">
+      <c r="B6" s="2" t="s">
         <v>13</v>
       </c>
       <c r="C6" s="0"/>
-      <c r="D6" s="5" t="s">
+      <c r="D6" s="0" t="s">
         <v>14</v>
       </c>
     </row>
@@ -554,11 +565,11 @@
       <c r="A7" s="0" t="s">
         <v>4</v>
       </c>
-      <c r="B7" s="6" t="s">
+      <c r="B7" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C7" s="0"/>
-      <c r="D7" s="5" t="s">
+      <c r="D7" s="0" t="s">
         <v>16</v>
       </c>
     </row>
@@ -566,11 +577,11 @@
       <c r="A8" s="0" t="s">
         <v>4</v>
       </c>
-      <c r="B8" s="6" t="s">
+      <c r="B8" s="2" t="s">
         <v>17</v>
       </c>
       <c r="C8" s="0"/>
-      <c r="D8" s="5" t="s">
+      <c r="D8" s="0" t="s">
         <v>18</v>
       </c>
     </row>
@@ -578,11 +589,11 @@
       <c r="A9" s="0" t="s">
         <v>4</v>
       </c>
-      <c r="B9" s="5" t="s">
+      <c r="B9" s="2" t="s">
         <v>19</v>
       </c>
       <c r="C9" s="0"/>
-      <c r="D9" s="5" t="s">
+      <c r="D9" s="0" t="s">
         <v>20</v>
       </c>
     </row>
@@ -590,11 +601,11 @@
       <c r="A10" s="0" t="s">
         <v>4</v>
       </c>
-      <c r="B10" s="5" t="s">
+      <c r="B10" s="2" t="s">
         <v>21</v>
       </c>
       <c r="C10" s="0"/>
-      <c r="D10" s="5" t="s">
+      <c r="D10" s="0" t="s">
         <v>22</v>
       </c>
     </row>
@@ -602,11 +613,11 @@
       <c r="A11" s="0" t="s">
         <v>4</v>
       </c>
-      <c r="B11" s="5" t="s">
+      <c r="B11" s="2" t="s">
         <v>23</v>
       </c>
       <c r="C11" s="0"/>
-      <c r="D11" s="5" t="s">
+      <c r="D11" s="0" t="s">
         <v>24</v>
       </c>
     </row>
@@ -614,11 +625,11 @@
       <c r="A12" s="0" t="s">
         <v>4</v>
       </c>
-      <c r="B12" s="7" t="s">
+      <c r="B12" s="5" t="s">
         <v>25</v>
       </c>
       <c r="C12" s="0"/>
-      <c r="D12" s="5" t="s">
+      <c r="D12" s="0" t="s">
         <v>26</v>
       </c>
     </row>
@@ -626,11 +637,11 @@
       <c r="A13" s="0" t="s">
         <v>4</v>
       </c>
-      <c r="B13" s="7" t="s">
+      <c r="B13" s="5" t="s">
         <v>27</v>
       </c>
       <c r="C13" s="0"/>
-      <c r="D13" s="5" t="s">
+      <c r="D13" s="0" t="s">
         <v>28</v>
       </c>
     </row>
@@ -638,11 +649,11 @@
       <c r="A14" s="0" t="s">
         <v>4</v>
       </c>
-      <c r="B14" s="5" t="s">
+      <c r="B14" s="2" t="s">
         <v>29</v>
       </c>
       <c r="C14" s="0"/>
-      <c r="D14" s="5" t="s">
+      <c r="D14" s="0" t="s">
         <v>30</v>
       </c>
     </row>
@@ -650,11 +661,11 @@
       <c r="A15" s="0" t="s">
         <v>4</v>
       </c>
-      <c r="B15" s="5" t="s">
+      <c r="B15" s="2" t="s">
         <v>31</v>
       </c>
       <c r="C15" s="0"/>
-      <c r="D15" s="5" t="s">
+      <c r="D15" s="0" t="s">
         <v>32</v>
       </c>
     </row>
@@ -662,11 +673,11 @@
       <c r="A16" s="0" t="s">
         <v>4</v>
       </c>
-      <c r="B16" s="1" t="s">
+      <c r="B16" s="2" t="s">
         <v>33</v>
       </c>
       <c r="C16" s="0"/>
-      <c r="D16" s="5" t="s">
+      <c r="D16" s="0" t="s">
         <v>34</v>
       </c>
     </row>
@@ -674,11 +685,11 @@
       <c r="A17" s="0" t="s">
         <v>4</v>
       </c>
-      <c r="B17" s="8" t="s">
+      <c r="B17" s="6" t="s">
         <v>35</v>
       </c>
       <c r="C17" s="0"/>
-      <c r="D17" s="5" t="s">
+      <c r="D17" s="0" t="s">
         <v>36</v>
       </c>
     </row>
@@ -686,11 +697,11 @@
       <c r="A18" s="0" t="s">
         <v>4</v>
       </c>
-      <c r="B18" s="8" t="s">
+      <c r="B18" s="6" t="s">
         <v>37</v>
       </c>
       <c r="C18" s="0"/>
-      <c r="D18" s="5" t="s">
+      <c r="D18" s="0" t="s">
         <v>38</v>
       </c>
     </row>
@@ -698,11 +709,11 @@
       <c r="A19" s="0" t="s">
         <v>4</v>
       </c>
-      <c r="B19" s="8" t="s">
+      <c r="B19" s="6" t="s">
         <v>39</v>
       </c>
       <c r="C19" s="0"/>
-      <c r="D19" s="5" t="s">
+      <c r="D19" s="0" t="s">
         <v>40</v>
       </c>
     </row>
@@ -710,323 +721,437 @@
       <c r="A20" s="0" t="s">
         <v>4</v>
       </c>
-      <c r="B20" s="8" t="s">
+      <c r="B20" s="6" t="s">
         <v>41</v>
       </c>
       <c r="C20" s="0"/>
-      <c r="D20" s="5" t="s">
+      <c r="D20" s="0" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="21" customFormat="false" ht="71" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="0" t="s">
         <v>4</v>
       </c>
-      <c r="B21" s="6" t="s">
+      <c r="B21" s="2" t="s">
         <v>43</v>
       </c>
       <c r="C21" s="0"/>
-      <c r="D21" s="5" t="s">
+      <c r="D21" s="2" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="22" customFormat="false" ht="105.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="0" t="s">
         <v>4</v>
       </c>
-      <c r="B22" s="6" t="s">
+      <c r="B22" s="2" t="s">
         <v>45</v>
       </c>
       <c r="C22" s="0"/>
-      <c r="D22" s="5" t="s">
+      <c r="D22" s="2" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="5" t="s">
+      <c r="A23" s="0" t="s">
+        <v>4</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="C23" s="0"/>
+      <c r="D23" s="0" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="0" t="s">
         <v>5</v>
       </c>
-      <c r="B23" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="C23" s="1" t="n">
+      <c r="B24" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="C24" s="0" t="n">
         <v>2</v>
       </c>
-    </row>
-    <row r="24" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="5" t="s">
+      <c r="D24" s="0"/>
+    </row>
+    <row r="25" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="0" t="s">
         <v>5</v>
       </c>
-      <c r="B24" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="C24" s="1" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="25" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="5" t="s">
+      <c r="B25" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="C25" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="D25" s="0"/>
+    </row>
+    <row r="26" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="0" t="s">
         <v>7</v>
       </c>
-      <c r="B25" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="C25" s="1" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="26" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="5" t="s">
+      <c r="B26" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="C26" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="D26" s="0"/>
+    </row>
+    <row r="27" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="0" t="s">
         <v>9</v>
       </c>
-      <c r="B26" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="C26" s="1" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="27" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="5" t="s">
+      <c r="B27" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="C27" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="D27" s="0"/>
+    </row>
+    <row r="28" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="0" t="s">
         <v>11</v>
       </c>
-      <c r="B27" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="C27" s="1" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="28" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="6" t="s">
+      <c r="B28" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="C28" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="D28" s="0"/>
+    </row>
+    <row r="29" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="B28" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="C28" s="1" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="29" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="6" t="s">
+      <c r="B29" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="C29" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="D29" s="0"/>
+    </row>
+    <row r="30" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="B29" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="C29" s="1" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="30" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="6" t="s">
+      <c r="B30" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="C30" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="D30" s="0"/>
+    </row>
+    <row r="31" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="B30" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="C30" s="1" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="31" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="5" t="s">
+      <c r="B31" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="C31" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="D31" s="0"/>
+    </row>
+    <row r="32" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="0" t="s">
         <v>19</v>
       </c>
-      <c r="B31" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="C31" s="1" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="32" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="5" t="s">
+      <c r="B32" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="C32" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="D32" s="0"/>
+    </row>
+    <row r="33" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="0" t="s">
         <v>21</v>
       </c>
-      <c r="B32" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="C32" s="1" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="33" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="5" t="s">
+      <c r="B33" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="C33" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="D33" s="0"/>
+    </row>
+    <row r="34" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="0" t="s">
         <v>23</v>
       </c>
-      <c r="B33" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="C33" s="1" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="34" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="7" t="s">
+      <c r="B34" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="C34" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="D34" s="0"/>
+    </row>
+    <row r="35" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="B34" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="C34" s="1" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="35" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="7" t="s">
+      <c r="B35" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="C35" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="D35" s="0"/>
+    </row>
+    <row r="36" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A36" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="B35" s="7" t="s">
-        <v>59</v>
-      </c>
-      <c r="C35" s="1" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="36" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="B36" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="C36" s="1" t="n">
-        <v>1</v>
-      </c>
+      <c r="B36" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="C36" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="D36" s="0"/>
     </row>
     <row r="37" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="B37" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="C37" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="D37" s="0"/>
+    </row>
+    <row r="38" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A38" s="0" t="s">
         <v>29</v>
       </c>
-      <c r="B37" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="C37" s="1" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="38" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="5" t="s">
+      <c r="B38" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="C38" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="D38" s="0"/>
+    </row>
+    <row r="39" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A39" s="0" t="s">
         <v>29</v>
       </c>
-      <c r="B38" s="9" t="s">
-        <v>62</v>
-      </c>
-      <c r="C38" s="1" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="39" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="5" t="s">
+      <c r="B39" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="C39" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="D39" s="0"/>
+    </row>
+    <row r="40" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A40" s="0" t="s">
         <v>31</v>
       </c>
-      <c r="B39" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="C39" s="1" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="40" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="1" t="s">
+      <c r="B40" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="C40" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="D40" s="0"/>
+    </row>
+    <row r="41" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A41" s="0" t="s">
         <v>33</v>
       </c>
-      <c r="B40" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="C40" s="1" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="41" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="8" t="s">
+      <c r="B41" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="C41" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="D41" s="0"/>
+    </row>
+    <row r="42" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A42" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="B41" s="10" t="s">
-        <v>65</v>
-      </c>
-      <c r="C41" s="1" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="42" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="8" t="s">
+      <c r="B42" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="C42" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="D42" s="0"/>
+    </row>
+    <row r="43" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A43" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="B42" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="C42" s="1" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="43" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="8" t="s">
+      <c r="B43" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C43" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="D43" s="0"/>
+    </row>
+    <row r="44" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A44" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="B43" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="C43" s="1" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="44" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="8" t="s">
+      <c r="B44" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="C44" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="D44" s="0"/>
+    </row>
+    <row r="45" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A45" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="B44" s="7" t="s">
-        <v>68</v>
-      </c>
-      <c r="C44" s="1" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="45" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="B45" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="C45" s="1" t="n">
-        <v>1</v>
-      </c>
+      <c r="B45" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="C45" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="D45" s="0"/>
     </row>
     <row r="46" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="B46" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="C46" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="D46" s="0"/>
+    </row>
+    <row r="47" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A47" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="B46" s="6" t="s">
+      <c r="B47" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="C46" s="1" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="47" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="6" t="s">
+      <c r="C47" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="D47" s="0"/>
+    </row>
+    <row r="48" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A48" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="B47" s="6" t="s">
+      <c r="B48" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="C47" s="1" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="48" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="49" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="50" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="51" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="52" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="53" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="54" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="55" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="56" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="57" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+      <c r="C48" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="D48" s="0"/>
+    </row>
+    <row r="49" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A49" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="B49" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="C49" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="D49" s="0"/>
+    </row>
+    <row r="50" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A50" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="B50" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="C50" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="D50" s="0"/>
+    </row>
+    <row r="51" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A51" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="B51" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="C51" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="D51" s="0"/>
+    </row>
+    <row r="52" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A52" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="B52" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="C52" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="D52" s="0"/>
+    </row>
+    <row r="53" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A53" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="B53" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="C53" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="D53" s="0"/>
+    </row>
+    <row r="54" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A54" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="B54" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="C54" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="D54" s="0"/>
+    </row>
+    <row r="55" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A55" s="0"/>
+      <c r="C55" s="0"/>
+      <c r="D55" s="0"/>
+    </row>
+    <row r="56" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A56" s="0"/>
+      <c r="C56" s="0"/>
+      <c r="D56" s="0"/>
+    </row>
+    <row r="57" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A57" s="0"/>
+      <c r="C57" s="0"/>
+      <c r="D57" s="0"/>
+    </row>
     <row r="58" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="59" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="60" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
@@ -1035,8 +1160,8 @@
     <row r="63" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="64" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="65" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="66" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="67" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048575" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048576" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
